--- a/data/trans_orig/P25A$medico-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P25A$medico-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según motivo para dejar de fumar (multirrespuesta) en 2007</t>
+          <t>Población según motivo para dejar de fumar (multirrespuesta) en 2007 (tasa de respuesta: 98,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22913</t>
+          <t>22483</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41076</t>
+          <t>40966</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>903</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7987</t>
+          <t>7765</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24884</t>
+          <t>25218</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44648</t>
+          <t>45974</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,93%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10407</t>
+          <t>9974</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26074</t>
+          <t>25344</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6607</t>
+          <t>5786</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11600</t>
+          <t>11620</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27229</t>
+          <t>28467</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,67%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5720</t>
+          <t>5694</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17985</t>
+          <t>17585</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7917</t>
+          <t>7040</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6751</t>
+          <t>7725</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20626</t>
+          <t>21939</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>962</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8048</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>848</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6884</t>
+          <t>6849</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12072</t>
+          <t>11780</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>73534</t>
+          <t>72985</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>94312</t>
+          <t>94605</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24924</t>
+          <t>24471</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>35583</t>
+          <t>35524</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>102329</t>
+          <t>101629</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>125830</t>
+          <t>126214</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,92%</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>980</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8455</t>
+          <t>10037</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10119</t>
+          <t>9830</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1367,12 +1367,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>3158</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>15176</t>
+          <t>15019</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39980</t>
+          <t>40402</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63151</t>
+          <t>64355</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1836</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11268</t>
+          <t>11140</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44956</t>
+          <t>44702</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70936</t>
+          <t>71137</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,97%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22509</t>
+          <t>23678</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44393</t>
+          <t>44441</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>4174</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15761</t>
+          <t>16104</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>30646</t>
+          <t>29584</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>56210</t>
+          <t>54496</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>20,66%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6763</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20282</t>
+          <t>20457</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4078</t>
+          <t>4223</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15638</t>
+          <t>15864</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13092</t>
+          <t>13190</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>32857</t>
+          <t>32025</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>4733</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15855</t>
+          <t>16603</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6083</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>5034</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18433</t>
+          <t>18419</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>91526</t>
+          <t>91804</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>118618</t>
+          <t>119996</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>45373</t>
+          <t>44339</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62154</t>
+          <t>62015</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>142314</t>
+          <t>143312</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>173673</t>
+          <t>176282</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>66,83%</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1884</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11583</t>
+          <t>11136</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>6105</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20849</t>
+          <t>19857</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>10085</t>
+          <t>10508</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>26229</t>
+          <t>28121</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22035</t>
+          <t>22173</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42206</t>
+          <t>41329</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>7495</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23979</t>
+          <t>22513</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43883</t>
+          <t>43060</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17473</t>
+          <t>17193</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35869</t>
+          <t>35733</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11508</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21561</t>
+          <t>22000</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>42097</t>
+          <t>41505</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>23,86%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7837</t>
+          <t>7693</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22549</t>
+          <t>22654</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10162</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>10970</t>
+          <t>10676</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>26721</t>
+          <t>27643</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6939</t>
+          <t>7205</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>922</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8284</t>
+          <t>8279</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11223</t>
+          <t>11343</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>65729</t>
+          <t>64952</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>89022</t>
+          <t>88512</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,29%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19737</t>
+          <t>20567</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>31279</t>
+          <t>31545</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>91700</t>
+          <t>88928</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>117038</t>
+          <t>115973</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>66,66%</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>6842</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1747</t>
+          <t>1748</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9779</t>
+          <t>9585</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2731,12 +2731,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2870</t>
+          <t>2806</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>12982</t>
+          <t>12980</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43869</t>
+          <t>43900</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>67552</t>
+          <t>67750</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5865</t>
+          <t>6132</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18434</t>
+          <t>19462</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>52688</t>
+          <t>54798</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>81094</t>
+          <t>82375</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,88%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>34343</t>
+          <t>32979</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>55265</t>
+          <t>55870</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13309</t>
+          <t>12971</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>29668</t>
+          <t>27513</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>51472</t>
+          <t>51131</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>77330</t>
+          <t>77170</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,92%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6126</t>
+          <t>5813</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18139</t>
+          <t>17848</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11716</t>
+          <t>11223</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10174</t>
+          <t>9620</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>25639</t>
+          <t>25789</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>2563</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11021</t>
+          <t>12061</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11721</t>
+          <t>10629</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,47 +3167,47 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>11,45%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>11031</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>5695</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>17837</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>4,13%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>2,13%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>12,63%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>11031</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>5647</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>18683</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>4,13%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>80595</t>
+          <t>79932</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>105485</t>
+          <t>105867</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>45905</t>
+          <t>46438</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>65395</t>
+          <t>65064</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>133397</t>
+          <t>131726</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>162662</t>
+          <t>163654</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>61,34%</t>
         </is>
       </c>
     </row>
@@ -3343,12 +3343,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>859</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>10042</t>
+          <t>12045</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>12262</t>
+          <t>13425</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4946</t>
+          <t>4646</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>19307</t>
+          <t>18231</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>146547</t>
+          <t>148595</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>191499</t>
+          <t>191333</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13395</t>
+          <t>12894</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>33379</t>
+          <t>30914</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>166235</t>
+          <t>166517</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>214789</t>
+          <t>214680</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,53%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>98278</t>
+          <t>99837</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>136992</t>
+          <t>137503</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>26066</t>
+          <t>25904</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>48311</t>
+          <t>47492</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>133501</t>
+          <t>132571</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>178395</t>
+          <t>176070</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,12%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>36167</t>
+          <t>35340</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>62083</t>
+          <t>63240</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>13204</t>
+          <t>12250</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>31723</t>
+          <t>30475</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>53133</t>
+          <t>52820</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>86402</t>
+          <t>86850</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>13128</t>
+          <t>12841</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>30466</t>
+          <t>29474</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>7348</t>
+          <t>6940</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>21121</t>
+          <t>21806</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>23317</t>
+          <t>23224</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>43831</t>
+          <t>43983</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>334485</t>
+          <t>334505</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>382759</t>
+          <t>382484</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>150391</t>
+          <t>150536</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>181985</t>
+          <t>181390</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>494708</t>
+          <t>495184</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>553869</t>
+          <t>552332</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>63,1%</t>
         </is>
       </c>
     </row>
@@ -4025,12 +4025,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>8406</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>24022</t>
+          <t>24256</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4040,12 +4040,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4060,12 +4060,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>18170</t>
+          <t>18981</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>38337</t>
+          <t>39836</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4075,12 +4075,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4095,12 +4095,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>30420</t>
+          <t>30197</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>56623</t>
+          <t>55524</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4110,12 +4110,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según motivo para dejar de fumar (multirrespuesta) en 2012</t>
+          <t>Población según motivo para dejar de fumar (multirrespuesta) en 2012 (tasa de respuesta: 97,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15655</t>
+          <t>14971</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34013</t>
+          <t>33407</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>985</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9190</t>
+          <t>9173</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18888</t>
+          <t>19100</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39973</t>
+          <t>38357</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>7426</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22030</t>
+          <t>22103</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>7904</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9235</t>
+          <t>9523</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25301</t>
+          <t>24730</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9801</t>
+          <t>10360</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26665</t>
+          <t>27775</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11409</t>
+          <t>12109</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13444</t>
+          <t>14623</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>33086</t>
+          <t>33782</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7752</t>
+          <t>7757</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21106</t>
+          <t>21139</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>6914</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21845</t>
+          <t>22123</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>131304</t>
+          <t>129913</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>153956</t>
+          <t>154040</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>58519</t>
+          <t>58566</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>69001</t>
+          <t>69085</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>194290</t>
+          <t>194171</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>221280</t>
+          <t>221046</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,78%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>954</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8175</t>
+          <t>9025</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>945</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8878</t>
+          <t>8021</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>2047</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12277</t>
+          <t>12338</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35883</t>
+          <t>36281</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62386</t>
+          <t>62845</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6082</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20082</t>
+          <t>19111</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45465</t>
+          <t>46115</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>76090</t>
+          <t>76900</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,16%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21386</t>
+          <t>22110</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43795</t>
+          <t>42636</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4427</t>
+          <t>4375</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17733</t>
+          <t>17768</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29978</t>
+          <t>29821</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>54773</t>
+          <t>54775</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13544</t>
+          <t>13177</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33847</t>
+          <t>34237</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9299</t>
+          <t>9229</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15813</t>
+          <t>16192</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>37382</t>
+          <t>37736</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9100</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2167</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11716</t>
+          <t>11670</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4135</t>
+          <t>4269</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16415</t>
+          <t>15846</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>150383</t>
+          <t>149240</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>180463</t>
+          <t>179162</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>57820</t>
+          <t>59273</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76875</t>
+          <t>77947</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>216973</t>
+          <t>214584</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>251647</t>
+          <t>251335</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,43%</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5621,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8729</t>
+          <t>8591</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>3869</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15335</t>
+          <t>17069</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5316</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>19684</t>
+          <t>19957</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35405</t>
+          <t>34607</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>61573</t>
+          <t>59319</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3169</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14870</t>
+          <t>14773</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41165</t>
+          <t>42188</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>69607</t>
+          <t>69996</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,4%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11536</t>
+          <t>11284</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31762</t>
+          <t>30359</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1779</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11335</t>
+          <t>13039</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14925</t>
+          <t>15148</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35718</t>
+          <t>37600</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,65%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3998</t>
+          <t>4065</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16613</t>
+          <t>16112</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4478</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16620</t>
+          <t>16978</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>10005</t>
+          <t>9890</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>27707</t>
+          <t>26793</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,72%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10609</t>
+          <t>11268</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>960</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8321</t>
+          <t>8281</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3998</t>
+          <t>3960</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15934</t>
+          <t>15339</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>92418</t>
+          <t>94631</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>122805</t>
+          <t>122736</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>71517</t>
+          <t>71288</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>88395</t>
+          <t>88664</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>173767</t>
+          <t>172265</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>206685</t>
+          <t>203312</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>73,79%</t>
         </is>
       </c>
     </row>
@@ -6303,12 +6303,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>937</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7844</t>
+          <t>8268</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6318,12 +6318,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11209</t>
+          <t>10667</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6353,12 +6353,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3924</t>
+          <t>3951</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>15052</t>
+          <t>15424</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6388,12 +6388,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30951</t>
+          <t>31003</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>54639</t>
+          <t>55178</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4996</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18185</t>
+          <t>19551</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39895</t>
+          <t>40671</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>67892</t>
+          <t>67516</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,14%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13996</t>
+          <t>13372</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>33040</t>
+          <t>30949</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>10428</t>
+          <t>9133</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>27043</t>
+          <t>26666</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>28235</t>
+          <t>28377</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>53066</t>
+          <t>52478</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,43%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9402</t>
+          <t>8908</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24084</t>
+          <t>24864</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8012</t>
+          <t>7711</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22697</t>
+          <t>23051</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>20476</t>
+          <t>21140</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>41540</t>
+          <t>42847</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3836</t>
+          <t>3825</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16653</t>
+          <t>16149</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>949</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11281</t>
+          <t>10592</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6532</t>
+          <t>6715</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20995</t>
+          <t>22552</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>117176</t>
+          <t>117011</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>145893</t>
+          <t>145898</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>74747</t>
+          <t>74259</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>93570</t>
+          <t>93143</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>199052</t>
+          <t>199706</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>232906</t>
+          <t>234163</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>73,32%</t>
         </is>
       </c>
     </row>
@@ -6985,12 +6985,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3778</t>
+          <t>2974</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>17163</t>
+          <t>16341</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7000,12 +7000,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7020,12 +7020,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>957</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>8175</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7055,12 +7055,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>5124</t>
+          <t>5696</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>20610</t>
+          <t>20526</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>137926</t>
+          <t>138297</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>184183</t>
+          <t>185369</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>24372</t>
+          <t>24164</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>47132</t>
+          <t>47385</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>167872</t>
+          <t>169939</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>222191</t>
+          <t>222787</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>69519</t>
+          <t>69852</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>107720</t>
+          <t>104258</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>24537</t>
+          <t>23883</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>49587</t>
+          <t>48479</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>100155</t>
+          <t>100440</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>143504</t>
+          <t>145462</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>48967</t>
+          <t>48425</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>81135</t>
+          <t>80815</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>21379</t>
+          <t>20743</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>43687</t>
+          <t>43260</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>76504</t>
+          <t>76378</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>117461</t>
+          <t>117202</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>19923</t>
+          <t>20728</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>42768</t>
+          <t>43390</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>6864</t>
+          <t>6521</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>21879</t>
+          <t>20973</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>30754</t>
+          <t>30736</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>58175</t>
+          <t>57019</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>523706</t>
+          <t>520980</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>578177</t>
+          <t>577329</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>281802</t>
+          <t>282067</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>316349</t>
+          <t>314939</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>816026</t>
+          <t>815047</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>881413</t>
+          <t>880525</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,22%</t>
         </is>
       </c>
     </row>
@@ -7667,12 +7667,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>10634</t>
+          <t>9690</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>29115</t>
+          <t>27799</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7682,12 +7682,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>11097</t>
+          <t>12242</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>28684</t>
+          <t>29632</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>25667</t>
+          <t>25339</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>51431</t>
+          <t>49613</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según motivo para dejar de fumar (multirrespuesta) en 2016</t>
+          <t>Población según motivo para dejar de fumar (multirrespuesta) en 2016 (tasa de respuesta: 79,61%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10582</t>
+          <t>11429</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26119</t>
+          <t>26449</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>930</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8191</t>
+          <t>7259</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13272</t>
+          <t>13267</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30858</t>
+          <t>30378</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,66%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10801</t>
+          <t>10412</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25944</t>
+          <t>25825</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3670</t>
+          <t>4147</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14482</t>
+          <t>14199</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16808</t>
+          <t>17411</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34472</t>
+          <t>35533</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,66%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12956</t>
+          <t>12583</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7290</t>
+          <t>7489</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8297,7 +8297,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3902</t>
+          <t>4019</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16203</t>
+          <t>15891</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>4216</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16208</t>
+          <t>18022</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4948</t>
+          <t>5123</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4721</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17243</t>
+          <t>18654</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -8473,7 +8473,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>85570</t>
+          <t>86716</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27679</t>
+          <t>28537</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>42036</t>
+          <t>41574</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>97233</t>
+          <t>98892</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>124339</t>
+          <t>123719</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>71,92%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15578</t>
+          <t>13734</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1809</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11037</t>
+          <t>11266</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6448</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>19607</t>
+          <t>20815</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20252</t>
+          <t>20298</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41071</t>
+          <t>41129</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8738,7 +8738,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9337</t>
+          <t>9121</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23099</t>
+          <t>23458</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46481</t>
+          <t>46428</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,61%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16747</t>
+          <t>16680</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35625</t>
+          <t>35674</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9085</t>
+          <t>8238</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23171</t>
+          <t>22584</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>28575</t>
+          <t>29567</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>52799</t>
+          <t>52560</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,94%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19872</t>
+          <t>20661</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>41832</t>
+          <t>42050</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5567</t>
+          <t>5514</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17135</t>
+          <t>17085</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>29810</t>
+          <t>30570</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>52686</t>
+          <t>56442</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>21,41%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13157</t>
+          <t>12688</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>920</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8403</t>
+          <t>8448</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4032</t>
+          <t>4804</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16676</t>
+          <t>18959</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>95027</t>
+          <t>93017</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>120056</t>
+          <t>120032</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51964</t>
+          <t>53193</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>69399</t>
+          <t>69410</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>152191</t>
+          <t>152503</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>183752</t>
+          <t>184761</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>70,09%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10976</t>
+          <t>10611</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26599</t>
+          <t>26150</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3613</t>
+          <t>3603</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13466</t>
+          <t>13475</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>16631</t>
+          <t>17017</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>34811</t>
+          <t>35160</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31902</t>
+          <t>31426</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53959</t>
+          <t>54282</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6726</t>
+          <t>7132</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19764</t>
+          <t>20097</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>42181</t>
+          <t>43005</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>69204</t>
+          <t>68364</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>32,85%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21400</t>
+          <t>21202</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41869</t>
+          <t>41205</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9611</t>
+          <t>9624</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25151</t>
+          <t>25647</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>46904</t>
+          <t>48154</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>23,14%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8042</t>
+          <t>8788</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23217</t>
+          <t>24825</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11709</t>
+          <t>12795</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12607</t>
+          <t>12324</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>30592</t>
+          <t>30298</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,56%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10647</t>
+          <t>10977</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9283</t>
+          <t>9369</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4006</t>
+          <t>4076</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15403</t>
+          <t>16518</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>53102</t>
+          <t>53011</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>76146</t>
+          <t>76508</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>41498</t>
+          <t>42672</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>57791</t>
+          <t>58371</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>99986</t>
+          <t>99177</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>129583</t>
+          <t>128347</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>61,68%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4173</t>
+          <t>4163</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15597</t>
+          <t>16685</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>6729</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>19728</t>
+          <t>20280</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>13145</t>
+          <t>13184</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>30946</t>
+          <t>30985</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,89%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19500</t>
+          <t>20628</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38522</t>
+          <t>38787</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5254</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18038</t>
+          <t>18743</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28904</t>
+          <t>28694</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>52832</t>
+          <t>50786</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,07%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13996</t>
+          <t>14009</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>32056</t>
+          <t>33062</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11366</t>
+          <t>11327</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>27293</t>
+          <t>27569</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>30512</t>
+          <t>30154</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>54923</t>
+          <t>54524</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,32%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13677</t>
+          <t>14216</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>32227</t>
+          <t>32180</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,47 +10303,47 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
+          <t>8,05%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>18,23%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>9383</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>4413</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
           <t>7,75%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>18,26%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>9383</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>4172</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>16473</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>7,75%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>21563</t>
+          <t>22159</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>43315</t>
+          <t>43374</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,57%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6339</t>
+          <t>6126</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19130</t>
+          <t>19683</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3153</t>
+          <t>3132</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>14276</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12085</t>
+          <t>11981</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>28639</t>
+          <t>28742</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>103075</t>
+          <t>102623</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>127712</t>
+          <t>128263</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>76623</t>
+          <t>74856</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>97529</t>
+          <t>96135</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>185188</t>
+          <t>186539</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>217888</t>
+          <t>219383</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,72%</t>
         </is>
       </c>
     </row>
@@ -10627,12 +10627,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>15649</t>
+          <t>16286</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>34638</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10642,12 +10642,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10662,12 +10662,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>10780</t>
+          <t>11075</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>28191</t>
+          <t>28868</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10677,12 +10677,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10697,12 +10697,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>30419</t>
+          <t>30368</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>56922</t>
+          <t>56030</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10712,12 +10712,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>18,83%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>97643</t>
+          <t>98347</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>138260</t>
+          <t>139481</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>21270</t>
+          <t>20725</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>41895</t>
+          <t>41942</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>125999</t>
+          <t>126555</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>173037</t>
+          <t>170583</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,12%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>79415</t>
+          <t>78537</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>116761</t>
+          <t>115709</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>34529</t>
+          <t>34350</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>59203</t>
+          <t>59179</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>119428</t>
+          <t>117851</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>163504</t>
+          <t>163134</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,33%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>56644</t>
+          <t>58291</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>90187</t>
+          <t>90426</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>18524</t>
+          <t>18371</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>38153</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>83249</t>
+          <t>82691</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>121094</t>
+          <t>121724</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,93%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>21916</t>
+          <t>20534</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>44924</t>
+          <t>43484</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,49 +11098,49 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
+          <t>7,18%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>9209</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>24915</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
           <t>7,42%</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>16107</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>9618</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>25014</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>4,8%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>7,45%</t>
-        </is>
-      </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>45</t>
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>35259</t>
+          <t>33082</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>61580</t>
+          <t>59840</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>341428</t>
+          <t>340682</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>388135</t>
+          <t>387723</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>216088</t>
+          <t>216823</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>251543</t>
+          <t>250636</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>569218</t>
+          <t>568845</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>630305</t>
+          <t>627130</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>66,62%</t>
         </is>
       </c>
     </row>
@@ -11309,12 +11309,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>43893</t>
+          <t>43197</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>73216</t>
+          <t>71994</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11324,12 +11324,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11344,12 +11344,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>33090</t>
+          <t>31537</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>57877</t>
+          <t>56648</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11359,12 +11359,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>81630</t>
+          <t>82874</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>121487</t>
+          <t>120653</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11394,12 +11394,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,82%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P25A$medico-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P25A$medico-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22483</t>
+          <t>23095</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40966</t>
+          <t>41934</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>914</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7765</t>
+          <t>7892</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25218</t>
+          <t>25016</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45974</t>
+          <t>45618</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,72%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>10427</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25344</t>
+          <t>25438</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5786</t>
+          <t>5806</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11620</t>
+          <t>11520</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28467</t>
+          <t>28078</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,45%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5694</t>
+          <t>5693</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17585</t>
+          <t>17539</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7040</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7725</t>
+          <t>7748</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21939</t>
+          <t>21258</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>971</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>8388</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>867</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6849</t>
+          <t>7397</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>2778</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11780</t>
+          <t>12416</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>72985</t>
+          <t>72291</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>94605</t>
+          <t>93515</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24471</t>
+          <t>24163</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>35524</t>
+          <t>35418</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>58,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>101629</t>
+          <t>101770</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>126214</t>
+          <t>126216</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,93%</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>975</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10037</t>
+          <t>8479</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1312,12 +1312,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1884</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9830</t>
+          <t>10089</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1367,12 +1367,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3158</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>15019</t>
+          <t>14896</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40402</t>
+          <t>40857</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64355</t>
+          <t>66263</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>1878</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11140</t>
+          <t>11714</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44702</t>
+          <t>44080</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71137</t>
+          <t>70586</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,76%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23678</t>
+          <t>22757</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44441</t>
+          <t>44484</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>4114</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16104</t>
+          <t>15456</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29584</t>
+          <t>29095</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>54496</t>
+          <t>53317</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,21%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>6751</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20457</t>
+          <t>21257</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4223</t>
+          <t>4184</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15864</t>
+          <t>16644</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13190</t>
+          <t>13209</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>32025</t>
+          <t>31632</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4733</t>
+          <t>4103</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16603</t>
+          <t>16693</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5723</t>
+          <t>4663</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5034</t>
+          <t>5044</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18419</t>
+          <t>17350</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>91804</t>
+          <t>91524</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>119996</t>
+          <t>120690</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>44339</t>
+          <t>45282</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62015</t>
+          <t>62480</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>143312</t>
+          <t>142112</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>176282</t>
+          <t>174884</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>66,3%</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>1913</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11136</t>
+          <t>10884</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6105</t>
+          <t>6307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19857</t>
+          <t>19586</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>10508</t>
+          <t>10140</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>28121</t>
+          <t>27173</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22173</t>
+          <t>22359</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41329</t>
+          <t>41706</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7495</t>
+          <t>7747</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22513</t>
+          <t>23443</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43060</t>
+          <t>43577</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>25,05%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17193</t>
+          <t>16563</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35733</t>
+          <t>35384</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10804</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22000</t>
+          <t>22142</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>41505</t>
+          <t>42455</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,4%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7693</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22654</t>
+          <t>21576</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>993</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>9365</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>10676</t>
+          <t>10486</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>27643</t>
+          <t>27890</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,03%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7205</t>
+          <t>7230</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>900</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>8048</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11343</t>
+          <t>11924</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>64952</t>
+          <t>65533</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>88512</t>
+          <t>88546</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20567</t>
+          <t>19360</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>31545</t>
+          <t>31141</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>88928</t>
+          <t>90728</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>115973</t>
+          <t>117025</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>67,26%</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6842</t>
+          <t>6920</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1748</t>
+          <t>1756</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9585</t>
+          <t>10152</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2731,12 +2731,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>2735</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>12980</t>
+          <t>13108</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2746,12 +2746,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43900</t>
+          <t>43376</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>67750</t>
+          <t>69124</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6132</t>
+          <t>6066</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19462</t>
+          <t>18355</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>54798</t>
+          <t>53415</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>82375</t>
+          <t>81230</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,45%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>32979</t>
+          <t>33602</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>55870</t>
+          <t>55784</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>12971</t>
+          <t>13351</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>27513</t>
+          <t>29222</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>51131</t>
+          <t>51319</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>77170</t>
+          <t>77973</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>29,23%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5813</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17848</t>
+          <t>17989</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11223</t>
+          <t>11517</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>9620</t>
+          <t>9576</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>25789</t>
+          <t>25219</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2563</t>
+          <t>2518</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12061</t>
+          <t>11757</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10629</t>
+          <t>10877</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5695</t>
+          <t>5433</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>18059</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>79932</t>
+          <t>78647</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>105867</t>
+          <t>105923</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>46438</t>
+          <t>45949</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>65064</t>
+          <t>64902</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>131726</t>
+          <t>132769</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>163654</t>
+          <t>164815</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,77%</t>
         </is>
       </c>
     </row>
@@ -3343,12 +3343,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>854</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>12045</t>
+          <t>10038</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2131</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>13425</t>
+          <t>12857</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4646</t>
+          <t>4891</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>18231</t>
+          <t>18055</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>148595</t>
+          <t>148718</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>191333</t>
+          <t>190845</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12894</t>
+          <t>13457</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>30914</t>
+          <t>31506</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>166517</t>
+          <t>166531</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>214680</t>
+          <t>214916</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,55%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>99837</t>
+          <t>99299</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>137503</t>
+          <t>139156</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>25904</t>
+          <t>26767</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>47492</t>
+          <t>48486</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>132571</t>
+          <t>133355</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>176070</t>
+          <t>177937</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,33%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>35340</t>
+          <t>36141</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>63240</t>
+          <t>63195</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>12250</t>
+          <t>13218</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>30475</t>
+          <t>31847</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>52820</t>
+          <t>53517</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>86850</t>
+          <t>85331</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>12841</t>
+          <t>13057</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>29474</t>
+          <t>30053</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>6940</t>
+          <t>7051</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>21806</t>
+          <t>20533</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>23224</t>
+          <t>22869</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>43983</t>
+          <t>44669</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>334505</t>
+          <t>336313</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>382484</t>
+          <t>385026</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>150536</t>
+          <t>150598</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>181390</t>
+          <t>180176</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>495184</t>
+          <t>494299</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>552332</t>
+          <t>553554</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>63,24%</t>
         </is>
       </c>
     </row>
@@ -4025,12 +4025,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>24256</t>
+          <t>23471</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4040,12 +4040,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4060,12 +4060,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>18981</t>
+          <t>18728</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>39836</t>
+          <t>38528</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4075,12 +4075,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4095,12 +4095,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>30197</t>
+          <t>30810</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>55524</t>
+          <t>55759</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4110,12 +4110,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14971</t>
+          <t>15140</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33407</t>
+          <t>34233</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>996</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9173</t>
+          <t>9067</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19100</t>
+          <t>18309</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38357</t>
+          <t>38267</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,68%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7426</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22103</t>
+          <t>22183</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7904</t>
+          <t>8170</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9523</t>
+          <t>9541</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24730</t>
+          <t>26346</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10360</t>
+          <t>10312</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27775</t>
+          <t>26824</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12109</t>
+          <t>12238</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14623</t>
+          <t>13395</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>33782</t>
+          <t>32596</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,5%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7757</t>
+          <t>7694</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21139</t>
+          <t>22041</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6914</t>
+          <t>7659</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22123</t>
+          <t>22669</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>129913</t>
+          <t>130746</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>154040</t>
+          <t>154059</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>58566</t>
+          <t>58240</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>69085</t>
+          <t>68873</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>194171</t>
+          <t>194595</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>221046</t>
+          <t>219527</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,19%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>953</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8021</t>
+          <t>8093</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>2121</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12338</t>
+          <t>12774</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36281</t>
+          <t>36826</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62845</t>
+          <t>63619</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>6351</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19111</t>
+          <t>18909</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46115</t>
+          <t>46166</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>76900</t>
+          <t>76271</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>21,98%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22110</t>
+          <t>21851</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42636</t>
+          <t>44112</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4375</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17768</t>
+          <t>17399</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29821</t>
+          <t>30183</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>54775</t>
+          <t>55970</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,13%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13177</t>
+          <t>13234</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>34237</t>
+          <t>33212</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9229</t>
+          <t>7836</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16192</t>
+          <t>15437</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>37736</t>
+          <t>36766</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7971</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>2174</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11670</t>
+          <t>12314</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>4321</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15846</t>
+          <t>17330</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>149240</t>
+          <t>147994</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>179162</t>
+          <t>179902</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59273</t>
+          <t>58495</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>77947</t>
+          <t>76452</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>214584</t>
+          <t>215059</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>251335</t>
+          <t>251645</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,52%</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5621,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8591</t>
+          <t>8657</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3869</t>
+          <t>3218</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17069</t>
+          <t>15068</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>5412</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>19957</t>
+          <t>20612</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34607</t>
+          <t>35774</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59319</t>
+          <t>60006</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3119</t>
+          <t>3031</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14773</t>
+          <t>15202</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>42188</t>
+          <t>41224</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>69996</t>
+          <t>69167</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,1%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11284</t>
+          <t>12030</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30359</t>
+          <t>30503</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1779</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13039</t>
+          <t>11433</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15148</t>
+          <t>14405</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37600</t>
+          <t>37193</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,5%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4065</t>
+          <t>4127</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16112</t>
+          <t>15998</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4478</t>
+          <t>4604</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16978</t>
+          <t>16965</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9890</t>
+          <t>10571</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>26793</t>
+          <t>27657</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11268</t>
+          <t>10826</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>942</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8281</t>
+          <t>8750</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>4029</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15339</t>
+          <t>14760</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>94631</t>
+          <t>95708</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>122736</t>
+          <t>121883</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>71288</t>
+          <t>72066</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>88664</t>
+          <t>89335</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>172265</t>
+          <t>173925</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>203312</t>
+          <t>206124</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>74,81%</t>
         </is>
       </c>
     </row>
@@ -6303,12 +6303,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>926</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8268</t>
+          <t>7764</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>1958</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10667</t>
+          <t>11154</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6358,7 +6358,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3951</t>
+          <t>3534</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>15424</t>
+          <t>14963</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6388,12 +6388,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31003</t>
+          <t>31914</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>55178</t>
+          <t>55839</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6005</t>
+          <t>5906</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19551</t>
+          <t>18871</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>40671</t>
+          <t>40326</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>67516</t>
+          <t>68223</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,36%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13372</t>
+          <t>14037</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>30949</t>
+          <t>32209</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9133</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>26666</t>
+          <t>26848</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>28377</t>
+          <t>28415</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>52478</t>
+          <t>51837</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,23%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8908</t>
+          <t>9489</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24864</t>
+          <t>23982</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7711</t>
+          <t>7887</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23051</t>
+          <t>23136</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>21140</t>
+          <t>20361</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>42847</t>
+          <t>41815</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,09%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3825</t>
+          <t>3853</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16149</t>
+          <t>17242</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>953</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10592</t>
+          <t>10510</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6715</t>
+          <t>6597</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>22552</t>
+          <t>22303</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>117011</t>
+          <t>114512</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>145898</t>
+          <t>144930</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>74259</t>
+          <t>75029</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>93143</t>
+          <t>94033</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>199706</t>
+          <t>199113</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>234163</t>
+          <t>234014</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,28%</t>
         </is>
       </c>
     </row>
@@ -6985,12 +6985,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>3752</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>16341</t>
+          <t>17346</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7000,12 +7000,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7020,12 +7020,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>939</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>8149</t>
+          <t>8444</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7055,12 +7055,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>5696</t>
+          <t>5822</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>20526</t>
+          <t>20116</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>138297</t>
+          <t>138274</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>185369</t>
+          <t>185072</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>24164</t>
+          <t>23978</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>47385</t>
+          <t>46866</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>169939</t>
+          <t>169436</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>222787</t>
+          <t>221388</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,41%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>69852</t>
+          <t>70060</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>104258</t>
+          <t>105400</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>23883</t>
+          <t>23031</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>48479</t>
+          <t>48870</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>100440</t>
+          <t>99887</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>145462</t>
+          <t>144016</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>48425</t>
+          <t>48021</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>80815</t>
+          <t>80630</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>20743</t>
+          <t>21302</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>43260</t>
+          <t>45371</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>76378</t>
+          <t>76889</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>117202</t>
+          <t>116045</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>20728</t>
+          <t>21455</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>43390</t>
+          <t>43465</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>6521</t>
+          <t>7246</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>20973</t>
+          <t>23098</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>30736</t>
+          <t>31715</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>57019</t>
+          <t>59310</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>520980</t>
+          <t>521546</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>577329</t>
+          <t>576324</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>282067</t>
+          <t>283419</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>314939</t>
+          <t>315071</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>815047</t>
+          <t>817611</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>880525</t>
+          <t>883544</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,47%</t>
         </is>
       </c>
     </row>
@@ -7667,12 +7667,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>9690</t>
+          <t>8965</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>27799</t>
+          <t>27330</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7682,12 +7682,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>12242</t>
+          <t>11235</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>29632</t>
+          <t>29119</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>25339</t>
+          <t>24869</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>49613</t>
+          <t>48291</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -8021,7 +8021,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26449</t>
+          <t>26610</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7259</t>
+          <t>7455</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13267</t>
+          <t>13253</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30378</t>
+          <t>30662</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,83%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10412</t>
+          <t>10622</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25825</t>
+          <t>26461</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4147</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14199</t>
+          <t>14113</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17411</t>
+          <t>17255</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35533</t>
+          <t>35317</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,53%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2126</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12583</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>845</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7489</t>
+          <t>7649</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4019</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15891</t>
+          <t>15503</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4216</t>
+          <t>4140</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18022</t>
+          <t>17200</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>5473</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5021</t>
+          <t>4789</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18654</t>
+          <t>17186</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>65010</t>
+          <t>65272</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>86716</t>
+          <t>86022</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28537</t>
+          <t>27937</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>41574</t>
+          <t>42485</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>98892</t>
+          <t>98138</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>123719</t>
+          <t>123375</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>71,72%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>3152</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13734</t>
+          <t>13908</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1809</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11266</t>
+          <t>11495</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7174</t>
+          <t>6784</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>20815</t>
+          <t>21478</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,49%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20298</t>
+          <t>20767</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41129</t>
+          <t>40972</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>962</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9121</t>
+          <t>8814</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23458</t>
+          <t>22890</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46428</t>
+          <t>45121</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,12%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16680</t>
+          <t>16741</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35674</t>
+          <t>36364</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8238</t>
+          <t>8714</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22584</t>
+          <t>24130</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29567</t>
+          <t>28891</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>52560</t>
+          <t>52932</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,08%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20661</t>
+          <t>19956</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>42050</t>
+          <t>40817</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5514</t>
+          <t>5529</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17085</t>
+          <t>17912</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>30570</t>
+          <t>28762</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>56442</t>
+          <t>52960</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>20,09%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12688</t>
+          <t>12675</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>937</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8448</t>
+          <t>8584</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4804</t>
+          <t>4510</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18959</t>
+          <t>17101</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>93017</t>
+          <t>94111</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>120032</t>
+          <t>120102</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>53193</t>
+          <t>53096</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>69410</t>
+          <t>70066</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>152503</t>
+          <t>152192</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>184761</t>
+          <t>184516</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>70,0%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10611</t>
+          <t>10261</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26150</t>
+          <t>26363</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3603</t>
+          <t>3599</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13475</t>
+          <t>13285</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9318,7 +9318,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>17017</t>
+          <t>16577</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>35160</t>
+          <t>35910</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,62%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31426</t>
+          <t>30989</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54282</t>
+          <t>54243</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>7421</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20097</t>
+          <t>20276</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43005</t>
+          <t>41853</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>68364</t>
+          <t>67200</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,29%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21202</t>
+          <t>21792</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41205</t>
+          <t>41557</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9624</t>
+          <t>10008</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25647</t>
+          <t>25346</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48154</t>
+          <t>46976</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>22,57%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8788</t>
+          <t>8319</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24825</t>
+          <t>22715</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12795</t>
+          <t>11942</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12324</t>
+          <t>12818</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>30298</t>
+          <t>31411</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>15,09%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10977</t>
+          <t>11029</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9369</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4076</t>
+          <t>3428</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16518</t>
+          <t>15425</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>53011</t>
+          <t>52735</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>76508</t>
+          <t>76554</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>42672</t>
+          <t>42320</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58371</t>
+          <t>57959</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>99177</t>
+          <t>101063</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>128347</t>
+          <t>129992</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>62,47%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4163</t>
+          <t>4057</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16685</t>
+          <t>14849</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6729</t>
+          <t>6759</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>20280</t>
+          <t>21165</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>13184</t>
+          <t>13507</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>30985</t>
+          <t>30543</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,68%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20628</t>
+          <t>19225</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38787</t>
+          <t>37325</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5224</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18743</t>
+          <t>18085</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28694</t>
+          <t>28404</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>50786</t>
+          <t>52038</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,49%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14009</t>
+          <t>14777</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>33062</t>
+          <t>32452</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11327</t>
+          <t>11349</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>27569</t>
+          <t>28481</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>30154</t>
+          <t>30007</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>54524</t>
+          <t>53595</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14216</t>
+          <t>14465</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>32180</t>
+          <t>32161</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4413</t>
+          <t>4378</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16108</t>
+          <t>16787</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>22159</t>
+          <t>21758</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>43374</t>
+          <t>42562</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,3%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6126</t>
+          <t>6372</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19683</t>
+          <t>20614</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3132</t>
+          <t>3195</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14276</t>
+          <t>14844</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11981</t>
+          <t>11459</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>28742</t>
+          <t>28966</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>102623</t>
+          <t>104273</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>128263</t>
+          <t>127465</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>74856</t>
+          <t>76545</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>96135</t>
+          <t>96726</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>186539</t>
+          <t>185849</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>219383</t>
+          <t>218839</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>73,54%</t>
         </is>
       </c>
     </row>
@@ -10627,12 +10627,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>16286</t>
+          <t>15901</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>34638</t>
+          <t>35097</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10642,12 +10642,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10662,12 +10662,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>11075</t>
+          <t>10059</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>28868</t>
+          <t>27629</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10677,12 +10677,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10697,12 +10697,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>30368</t>
+          <t>30982</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>56030</t>
+          <t>56770</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10712,12 +10712,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,08%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>98347</t>
+          <t>98799</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>139481</t>
+          <t>136657</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>20725</t>
+          <t>20976</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>41942</t>
+          <t>41737</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>126555</t>
+          <t>125552</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>170583</t>
+          <t>172434</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,32%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>78537</t>
+          <t>77530</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>115709</t>
+          <t>115363</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>34350</t>
+          <t>33752</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>59179</t>
+          <t>58845</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>117851</t>
+          <t>120630</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>163134</t>
+          <t>164544</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,48%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>58291</t>
+          <t>56420</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>90426</t>
+          <t>89752</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>18371</t>
+          <t>18835</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>39684</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>82691</t>
+          <t>81514</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>121724</t>
+          <t>119615</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,71%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>20534</t>
+          <t>20699</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>43484</t>
+          <t>42437</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>9209</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>24915</t>
+          <t>25595</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>33082</t>
+          <t>34159</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>59840</t>
+          <t>61460</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>340682</t>
+          <t>341105</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>387723</t>
+          <t>387069</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>216823</t>
+          <t>218497</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>250636</t>
+          <t>250987</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>568845</t>
+          <t>567445</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>627130</t>
+          <t>628504</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,77%</t>
         </is>
       </c>
     </row>
@@ -11309,12 +11309,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>43197</t>
+          <t>44049</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>71994</t>
+          <t>73170</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11324,12 +11324,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11344,12 +11344,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>31537</t>
+          <t>30698</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>56648</t>
+          <t>57047</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11359,12 +11359,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>82874</t>
+          <t>81718</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>120653</t>
+          <t>119585</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11394,12 +11394,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,7%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P25A$medico-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P25A$medico-Habitat-trans_orig.xlsx
@@ -943,112 +943,112 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Preocupacion de sus efectos</t>
+          <t>Otros motivos</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10596</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5693</t>
+          <t>975</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17539</t>
+          <t>8479</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>4894</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7721</t>
+          <t>10089</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>12909</t>
+          <t>8017</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7748</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21258</t>
+          <t>14896</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -1056,112 +1056,112 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Disminucion del rendimiento físico/psíquico</t>
+          <t>Preocupacion de sus efectos</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3012</t>
+          <t>10596</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>5693</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8388</t>
+          <t>17539</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2839</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7397</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>12909</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>7748</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12416</t>
+          <t>21258</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -1169,112 +1169,112 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Propia voluntad</t>
+          <t>Disminucion del rendimiento físico/psíquico</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>83797</t>
+          <t>3012</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>72291</t>
+          <t>971</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>93515</t>
+          <t>8388</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>30615</t>
+          <t>2839</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24163</t>
+          <t>867</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>35418</t>
+          <t>7397</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>114412</t>
+          <t>5851</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>101770</t>
+          <t>2778</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>126216</t>
+          <t>12416</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -1282,112 +1282,112 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Otros motivos</t>
+          <t>Propia voluntad</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>83797</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>72291</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8479</t>
+          <t>93515</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4894</t>
+          <t>30615</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1830</t>
+          <t>24163</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10089</t>
+          <t>35418</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>58,51%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>113</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>8017</t>
+          <t>114412</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3924</t>
+          <t>101770</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>14896</t>
+          <t>126216</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>73,93%</t>
         </is>
       </c>
     </row>
@@ -1625,112 +1625,112 @@
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Preocupacion de sus efectos</t>
+          <t>Otros motivos</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5148</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1913</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>10884</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>5,83%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>12153</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6751</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>21257</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>6,5%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>3,61%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>11,38%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8818</t>
+          <t>12354</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4184</t>
+          <t>6307</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16644</t>
+          <t>19586</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>20971</t>
+          <t>17502</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13209</t>
+          <t>10140</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>31632</t>
+          <t>27173</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -1738,112 +1738,112 @@
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Disminucion del rendimiento físico/psíquico</t>
+          <t>Preocupacion de sus efectos</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8976</t>
+          <t>12153</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4103</t>
+          <t>6751</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16693</t>
+          <t>21257</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>8818</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4184</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4663</t>
+          <t>16644</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>10121</t>
+          <t>20971</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5044</t>
+          <t>13209</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17350</t>
+          <t>31632</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -1851,112 +1851,112 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Propia voluntad</t>
+          <t>Disminucion del rendimiento físico/psíquico</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>105498</t>
+          <t>8976</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>91524</t>
+          <t>4103</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>120690</t>
+          <t>16693</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>53677</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>45282</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62480</t>
+          <t>4663</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>159174</t>
+          <t>10121</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>142112</t>
+          <t>5044</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>174884</t>
+          <t>17350</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -1964,112 +1964,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Otros motivos</t>
+          <t>Propia voluntad</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>105498</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1913</t>
+          <t>91524</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10884</t>
+          <t>120690</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12354</t>
+          <t>53677</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6307</t>
+          <t>45282</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19586</t>
+          <t>62480</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>150</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>17502</t>
+          <t>159174</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>10140</t>
+          <t>142112</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>27173</t>
+          <t>174884</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>66,3%</t>
         </is>
       </c>
     </row>
@@ -2307,112 +2307,112 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Preocupacion de sus efectos</t>
+          <t>Otros motivos</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>13730</t>
+          <t>1885</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21576</t>
+          <t>6920</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4144</t>
+          <t>4633</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>1756</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9365</t>
+          <t>10152</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>17874</t>
+          <t>6518</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>10486</t>
+          <t>2735</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>27890</t>
+          <t>13108</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -2420,42 +2420,42 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Disminucion del rendimiento físico/psíquico</t>
+          <t>Preocupacion de sus efectos</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2037</t>
+          <t>13730</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7230</t>
+          <t>21576</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2465,67 +2465,67 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3587</t>
+          <t>4144</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>993</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8048</t>
+          <t>9365</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>5624</t>
+          <t>17874</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>10486</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11924</t>
+          <t>27890</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>16,03%</t>
         </is>
       </c>
     </row>
@@ -2533,112 +2533,112 @@
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Propia voluntad</t>
+          <t>Disminucion del rendimiento físico/psíquico</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>77071</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>65533</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>88546</t>
+          <t>7230</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>25983</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19360</t>
+          <t>900</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>31141</t>
+          <t>8048</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>103055</t>
+          <t>5624</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>90728</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>117025</t>
+          <t>11924</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -2646,112 +2646,112 @@
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Otros motivos</t>
+          <t>Propia voluntad</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>77071</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>65533</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6920</t>
+          <t>88546</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4633</t>
+          <t>25983</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1756</t>
+          <t>19360</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10152</t>
+          <t>31141</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>100</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>6518</t>
+          <t>103055</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2735</t>
+          <t>90728</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>13108</t>
+          <t>117025</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>67,26%</t>
         </is>
       </c>
     </row>
@@ -2989,42 +2989,42 @@
       <c r="A24" s="1" t="n"/>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Preocupacion de sus efectos</t>
+          <t>Otros motivos</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>11098</t>
+          <t>4158</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>854</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17989</t>
+          <t>10038</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3034,67 +3034,67 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>5606</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>2131</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11517</t>
+          <t>12857</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>16391</t>
+          <t>9763</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>9576</t>
+          <t>4891</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>25219</t>
+          <t>18055</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -3102,42 +3102,42 @@
       <c r="A25" s="1" t="n"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Disminucion del rendimiento físico/psíquico</t>
+          <t>Preocupacion de sus efectos</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>5958</t>
+          <t>11098</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2518</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11757</t>
+          <t>17989</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3147,22 +3147,22 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10877</t>
+          <t>11517</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3172,42 +3172,42 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>11031</t>
+          <t>16391</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5433</t>
+          <t>9576</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18059</t>
+          <t>25219</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -3215,112 +3215,112 @@
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Propia voluntad</t>
+          <t>Disminucion del rendimiento físico/psíquico</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>92583</t>
+          <t>5958</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>78647</t>
+          <t>2518</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>105923</t>
+          <t>11757</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>55569</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>45949</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>64902</t>
+          <t>10877</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>148152</t>
+          <t>11031</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>132769</t>
+          <t>5433</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>164815</t>
+          <t>18059</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -3328,112 +3328,112 @@
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Otros motivos</t>
+          <t>Propia voluntad</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>93</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>4158</t>
+          <t>92583</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>78647</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>10038</t>
+          <t>105923</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5606</t>
+          <t>55569</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>45949</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>12857</t>
+          <t>64902</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>146</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>9763</t>
+          <t>148152</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4891</t>
+          <t>132769</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>18055</t>
+          <t>164815</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>61,77%</t>
         </is>
       </c>
     </row>
@@ -3671,112 +3671,112 @@
       <c r="A30" s="1" t="n"/>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Preocupacion de sus efectos</t>
+          <t>Otros motivos</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>47577</t>
+          <t>14314</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>36141</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>63195</t>
+          <t>23471</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>20568</t>
+          <t>27487</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>13218</t>
+          <t>18728</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>31847</t>
+          <t>38528</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>40</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>68145</t>
+          <t>41800</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>53517</t>
+          <t>30810</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>85331</t>
+          <t>55759</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -3784,112 +3784,112 @@
       <c r="A31" s="1" t="n"/>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Disminucion del rendimiento físico/psíquico</t>
+          <t>Preocupacion de sus efectos</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>48</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>19983</t>
+          <t>47577</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>13057</t>
+          <t>36141</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>30053</t>
+          <t>63195</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>12643</t>
+          <t>20568</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>7051</t>
+          <t>13218</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>20533</t>
+          <t>31847</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>67</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>32626</t>
+          <t>68145</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>22869</t>
+          <t>53517</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>44669</t>
+          <t>85331</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -3897,112 +3897,112 @@
       <c r="A32" s="1" t="n"/>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Propia voluntad</t>
+          <t>Disminucion del rendimiento físico/psíquico</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>358950</t>
+          <t>19983</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>336313</t>
+          <t>13057</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>385026</t>
+          <t>30053</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>165844</t>
+          <t>12643</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>150598</t>
+          <t>7051</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>180176</t>
+          <t>20533</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>34</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>524794</t>
+          <t>32626</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>494299</t>
+          <t>22869</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>553554</t>
+          <t>44669</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -4010,112 +4010,112 @@
       <c r="A33" s="1" t="n"/>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Otros motivos</t>
+          <t>Propia voluntad</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>348</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>14314</t>
+          <t>358950</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>336313</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>23471</t>
+          <t>385026</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>161</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>27487</t>
+          <t>165844</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>18728</t>
+          <t>150598</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>38528</t>
+          <t>180176</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>509</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>41800</t>
+          <t>524794</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>30810</t>
+          <t>494299</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>55759</t>
+          <t>553554</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>63,24%</t>
         </is>
       </c>
     </row>
@@ -4585,112 +4585,112 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Preocupacion de sus efectos</t>
+          <t>Otros motivos</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17266</t>
+          <t>3053</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10312</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26824</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4954</t>
+          <t>2980</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1142</t>
+          <t>953</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12238</t>
+          <t>8093</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>22220</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13395</t>
+          <t>2121</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>32596</t>
+          <t>12774</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -4698,112 +4698,112 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Disminucion del rendimiento físico/psíquico</t>
+          <t>Preocupacion de sus efectos</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13310</t>
+          <t>17266</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7694</t>
+          <t>10312</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22041</t>
+          <t>26824</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4954</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12238</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>13310</t>
+          <t>22220</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7659</t>
+          <t>13395</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22669</t>
+          <t>32596</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>12,5%</t>
         </is>
       </c>
     </row>
@@ -4811,112 +4811,112 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Propia voluntad</t>
+          <t>Disminucion del rendimiento físico/psíquico</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>143262</t>
+          <t>13310</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>130746</t>
+          <t>7694</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>154059</t>
+          <t>22041</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>64808</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>58240</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>68873</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>208070</t>
+          <t>13310</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>194595</t>
+          <t>7659</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>219527</t>
+          <t>22669</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -4924,112 +4924,112 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Otros motivos</t>
+          <t>Propia voluntad</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>136</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3053</t>
+          <t>143262</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>130746</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>154059</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2980</t>
+          <t>64808</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>58240</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8093</t>
+          <t>68873</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>197</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>208070</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>194595</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12774</t>
+          <t>219527</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>84,19%</t>
         </is>
       </c>
     </row>
@@ -5267,112 +5267,112 @@
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Preocupacion de sus efectos</t>
+          <t>Otros motivos</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21730</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13234</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33212</t>
+          <t>8657</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3250</t>
+          <t>8095</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>3218</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7836</t>
+          <t>15068</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>24980</t>
+          <t>11282</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15437</t>
+          <t>5412</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>36766</t>
+          <t>20612</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -5380,112 +5380,112 @@
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Disminucion del rendimiento físico/psíquico</t>
+          <t>Preocupacion de sus efectos</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>21730</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>13234</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>33212</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8,74%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,32%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>13,35%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>3318</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1044</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>10117</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,07%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5583</t>
+          <t>3250</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2174</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12314</t>
+          <t>7836</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>8901</t>
+          <t>24980</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4321</t>
+          <t>15437</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17330</t>
+          <t>36766</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -5493,112 +5493,112 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Propia voluntad</t>
+          <t>Disminucion del rendimiento físico/psíquico</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>165678</t>
+          <t>3318</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>147994</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>179902</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>68510</t>
+          <t>5583</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>58495</t>
+          <t>2174</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76452</t>
+          <t>12314</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>234187</t>
+          <t>8901</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>215059</t>
+          <t>4321</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>251645</t>
+          <t>17330</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -5606,112 +5606,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Otros motivos</t>
+          <t>Propia voluntad</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>154</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3187</t>
+          <t>165678</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>147994</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8657</t>
+          <t>179902</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8095</t>
+          <t>68510</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3218</t>
+          <t>58495</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15068</t>
+          <t>76452</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>217</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>11282</t>
+          <t>234187</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>5412</t>
+          <t>215059</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>20612</t>
+          <t>251645</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>72,52%</t>
         </is>
       </c>
     </row>
@@ -5949,112 +5949,112 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Preocupacion de sus efectos</t>
+          <t>Otros motivos</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2877</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>926</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>7764</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>4,5%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>5036</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1958</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>11154</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>4,88%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>10,81%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>8564</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>4127</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>15998</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>4,97%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>9,28%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>9084</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>4604</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>16965</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>8,8%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>4,46%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>16,44%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>17648</t>
+          <t>7913</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>10571</t>
+          <t>3534</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>27657</t>
+          <t>14963</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -6062,112 +6062,112 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Disminucion del rendimiento físico/psíquico</t>
+          <t>Preocupacion de sus efectos</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5127</t>
+          <t>8564</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>4127</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10826</t>
+          <t>15998</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>9084</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>4604</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8750</t>
+          <t>16965</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>8208</t>
+          <t>17648</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4029</t>
+          <t>10571</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14760</t>
+          <t>27657</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -6175,112 +6175,112 @@
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Propia voluntad</t>
+          <t>Disminucion del rendimiento físico/psíquico</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>108633</t>
+          <t>5127</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>95708</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>121883</t>
+          <t>10826</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>81414</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>72066</t>
+          <t>942</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>89335</t>
+          <t>8750</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>190046</t>
+          <t>8208</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>173925</t>
+          <t>4029</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>206124</t>
+          <t>14760</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -6288,112 +6288,112 @@
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Otros motivos</t>
+          <t>Propia voluntad</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2877</t>
+          <t>108633</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>95708</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7764</t>
+          <t>121883</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>71</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5036</t>
+          <t>81414</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1958</t>
+          <t>72066</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11154</t>
+          <t>89335</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>168</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>7913</t>
+          <t>190046</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3534</t>
+          <t>173925</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>14963</t>
+          <t>206124</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>74,81%</t>
         </is>
       </c>
     </row>
@@ -6631,112 +6631,112 @@
       <c r="A24" s="1" t="n"/>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Preocupacion de sus efectos</t>
+          <t>Otros motivos</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>15689</t>
+          <t>8028</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9489</t>
+          <t>3752</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>23982</t>
+          <t>17346</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>14074</t>
+          <t>3033</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7887</t>
+          <t>939</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23136</t>
+          <t>8444</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>29763</t>
+          <t>11060</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>20361</t>
+          <t>5822</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>41815</t>
+          <t>20116</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -6744,112 +6744,112 @@
       <c r="A25" s="1" t="n"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Disminucion del rendimiento físico/psíquico</t>
+          <t>Preocupacion de sus efectos</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>8661</t>
+          <t>15689</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3853</t>
+          <t>9489</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17242</t>
+          <t>23982</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3723</t>
+          <t>14074</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>7887</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10510</t>
+          <t>23136</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>29</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>12384</t>
+          <t>29763</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6597</t>
+          <t>20361</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>22303</t>
+          <t>41815</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>13,09%</t>
         </is>
       </c>
     </row>
@@ -6857,112 +6857,112 @@
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Propia voluntad</t>
+          <t>Disminucion del rendimiento físico/psíquico</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>132001</t>
+          <t>8661</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>114512</t>
+          <t>3853</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>144930</t>
+          <t>17242</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>84924</t>
+          <t>3723</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>75029</t>
+          <t>953</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>94033</t>
+          <t>10510</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>216924</t>
+          <t>12384</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>199113</t>
+          <t>6597</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>234014</t>
+          <t>22303</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -6970,112 +6970,112 @@
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Otros motivos</t>
+          <t>Propia voluntad</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>125</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>8028</t>
+          <t>132001</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3752</t>
+          <t>114512</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>17346</t>
+          <t>144930</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>63,96%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>78</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3033</t>
+          <t>84924</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>75029</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>8444</t>
+          <t>94033</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>203</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>11060</t>
+          <t>216924</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>5822</t>
+          <t>199113</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>20116</t>
+          <t>234014</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>73,28%</t>
         </is>
       </c>
     </row>
@@ -7313,112 +7313,112 @@
       <c r="A30" s="1" t="n"/>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Preocupacion de sus efectos</t>
+          <t>Otros motivos</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>63249</t>
+          <t>17144</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>48021</t>
+          <t>8965</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>80630</t>
+          <t>27330</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>31362</t>
+          <t>19143</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>21302</t>
+          <t>11235</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>45371</t>
+          <t>29119</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>34</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>94611</t>
+          <t>36288</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>76889</t>
+          <t>24869</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>116045</t>
+          <t>48291</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -7426,112 +7426,112 @@
       <c r="A31" s="1" t="n"/>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Disminucion del rendimiento físico/psíquico</t>
+          <t>Preocupacion de sus efectos</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>58</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>30416</t>
+          <t>63249</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>21455</t>
+          <t>48021</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>43465</t>
+          <t>80630</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>12387</t>
+          <t>31362</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>7246</t>
+          <t>21302</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>23098</t>
+          <t>45371</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>86</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>42803</t>
+          <t>94611</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>31715</t>
+          <t>76889</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>59310</t>
+          <t>116045</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -7539,112 +7539,112 @@
       <c r="A32" s="1" t="n"/>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Propia voluntad</t>
+          <t>Disminucion del rendimiento físico/psíquico</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>549572</t>
+          <t>30416</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>521546</t>
+          <t>21455</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>576324</t>
+          <t>43465</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>299655</t>
+          <t>12387</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>283419</t>
+          <t>7246</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>315071</t>
+          <t>23098</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>40</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>849228</t>
+          <t>42803</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>817611</t>
+          <t>31715</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>883544</t>
+          <t>59310</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -7652,112 +7652,112 @@
       <c r="A33" s="1" t="n"/>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Otros motivos</t>
+          <t>Propia voluntad</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>512</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>17144</t>
+          <t>549572</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>8965</t>
+          <t>521546</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>27330</t>
+          <t>576324</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>273</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>19143</t>
+          <t>299655</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>11235</t>
+          <t>283419</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>29119</t>
+          <t>315071</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>785</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>36288</t>
+          <t>849228</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>24869</t>
+          <t>817611</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>48291</t>
+          <t>883544</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>73,47%</t>
         </is>
       </c>
     </row>
@@ -8227,112 +8227,112 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Preocupacion de sus efectos</t>
+          <t>Otros motivos</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7182</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3152</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>13908</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>6,08%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>11,77%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>5727</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2126</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>12848</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,85%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>10,87%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>5197</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7649</t>
+          <t>11495</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>8539</t>
+          <t>12379</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3846</t>
+          <t>6784</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15503</t>
+          <t>21478</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>12,49%</t>
         </is>
       </c>
     </row>
@@ -8340,112 +8340,112 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Disminucion del rendimiento físico/psíquico</t>
+          <t>Preocupacion de sus efectos</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5727</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2126</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,85%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10,87%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2812</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>845</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7649</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>5,23%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>14,22%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>8905</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4140</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>17200</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>7,53%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>14,55%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>974</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5473</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>10,17%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>9879</t>
+          <t>8539</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4789</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17186</t>
+          <t>15503</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -8453,112 +8453,112 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Propia voluntad</t>
+          <t>Disminucion del rendimiento físico/psíquico</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>76017</t>
+          <t>8905</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>65272</t>
+          <t>4140</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>86022</t>
+          <t>17200</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>35477</t>
+          <t>974</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27937</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>42485</t>
+          <t>5473</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>111494</t>
+          <t>9879</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>98138</t>
+          <t>4789</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>123375</t>
+          <t>17186</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -8566,112 +8566,112 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Otros motivos</t>
+          <t>Propia voluntad</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7182</t>
+          <t>76017</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>65272</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13908</t>
+          <t>86022</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5197</t>
+          <t>35477</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>27937</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11495</t>
+          <t>42485</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>108</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>12379</t>
+          <t>111494</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6784</t>
+          <t>98138</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>21478</t>
+          <t>123375</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>71,72%</t>
         </is>
       </c>
     </row>
@@ -8909,112 +8909,112 @@
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Preocupacion de sus efectos</t>
+          <t>Otros motivos</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>29901</t>
+          <t>17406</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19956</t>
+          <t>10261</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>40817</t>
+          <t>26363</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10337</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5529</t>
+          <t>3599</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17912</t>
+          <t>13285</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>25</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>40238</t>
+          <t>24720</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>28762</t>
+          <t>16577</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>52960</t>
+          <t>35910</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>13,62%</t>
         </is>
       </c>
     </row>
@@ -9022,112 +9022,112 @@
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Disminucion del rendimiento físico/psíquico</t>
+          <t>Preocupacion de sus efectos</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5662</t>
+          <t>29901</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>19956</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12675</t>
+          <t>40817</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3700</t>
+          <t>10337</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>5529</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8584</t>
+          <t>17912</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>38</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>9363</t>
+          <t>40238</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4510</t>
+          <t>28762</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17101</t>
+          <t>52960</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>20,09%</t>
         </is>
       </c>
     </row>
@@ -9135,112 +9135,112 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Propia voluntad</t>
+          <t>Disminucion del rendimiento físico/psíquico</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>107474</t>
+          <t>5662</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>94111</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>120102</t>
+          <t>12675</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>61537</t>
+          <t>3700</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>53096</t>
+          <t>937</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70066</t>
+          <t>8584</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>169011</t>
+          <t>9363</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>152192</t>
+          <t>4510</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>184516</t>
+          <t>17101</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -9248,112 +9248,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Otros motivos</t>
+          <t>Propia voluntad</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>102</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17406</t>
+          <t>107474</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10261</t>
+          <t>94111</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26363</t>
+          <t>120102</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7315</t>
+          <t>61537</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3599</t>
+          <t>53096</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13285</t>
+          <t>70066</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>160</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>24720</t>
+          <t>169011</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>16577</t>
+          <t>152192</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>35910</t>
+          <t>184516</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>70,0%</t>
         </is>
       </c>
     </row>
@@ -9591,112 +9591,112 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Preocupacion de sus efectos</t>
+          <t>Otros motivos</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>14891</t>
+          <t>8576</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8319</t>
+          <t>4057</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22715</t>
+          <t>14849</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4930</t>
+          <t>12429</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>6759</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11942</t>
+          <t>21165</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>19820</t>
+          <t>21004</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12818</t>
+          <t>13507</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>31411</t>
+          <t>30543</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,68%</t>
         </is>
       </c>
     </row>
@@ -9704,112 +9704,112 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Disminucion del rendimiento físico/psíquico</t>
+          <t>Preocupacion de sus efectos</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>14891</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>8319</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>22715</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>11,15%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>6,23%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>17,01%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>4396</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1035</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>11029</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>3,29%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>8,26%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4027</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>11942</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>8423</t>
+          <t>19820</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3428</t>
+          <t>12818</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15425</t>
+          <t>31411</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>15,09%</t>
         </is>
       </c>
     </row>
@@ -9817,112 +9817,112 @@
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Propia voluntad</t>
+          <t>Disminucion del rendimiento físico/psíquico</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>64433</t>
+          <t>4396</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>52735</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>76554</t>
+          <t>11029</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,33%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>50331</t>
+          <t>4027</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>42320</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>57959</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>114764</t>
+          <t>8423</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>101063</t>
+          <t>3428</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>129992</t>
+          <t>15425</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -9930,112 +9930,112 @@
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Otros motivos</t>
+          <t>Propia voluntad</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8576</t>
+          <t>64433</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>52735</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14849</t>
+          <t>76554</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12429</t>
+          <t>50331</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6759</t>
+          <t>42320</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>21165</t>
+          <t>57959</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>112</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>21004</t>
+          <t>114764</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>13507</t>
+          <t>101063</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>30543</t>
+          <t>129992</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>62,47%</t>
         </is>
       </c>
     </row>
@@ -10273,112 +10273,112 @@
       <c r="A24" s="1" t="n"/>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Preocupacion de sus efectos</t>
+          <t>Otros motivos</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>21983</t>
+          <t>24163</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14465</t>
+          <t>15901</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>32161</t>
+          <t>35097</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>9383</t>
+          <t>18320</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4378</t>
+          <t>10059</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16787</t>
+          <t>27629</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>38</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>31366</t>
+          <t>42483</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>21758</t>
+          <t>30982</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>42562</t>
+          <t>56770</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>19,08%</t>
         </is>
       </c>
     </row>
@@ -10386,112 +10386,112 @@
       <c r="A25" s="1" t="n"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Disminucion del rendimiento físico/psíquico</t>
+          <t>Preocupacion de sus efectos</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>11421</t>
+          <t>21983</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6372</t>
+          <t>14465</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20614</t>
+          <t>32161</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>8,2%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>18,22%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>9383</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>4378</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>16787</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>7,75%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
           <t>3,61%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>11,68%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>7406</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>3195</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>14844</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>6,11%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>2,64%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>30</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>18826</t>
+          <t>31366</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11459</t>
+          <t>21758</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>28966</t>
+          <t>42562</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>14,3%</t>
         </is>
       </c>
     </row>
@@ -10499,112 +10499,112 @@
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Propia voluntad</t>
+          <t>Disminucion del rendimiento físico/psíquico</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>116398</t>
+          <t>11421</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>104273</t>
+          <t>6372</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>127465</t>
+          <t>20614</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>86937</t>
+          <t>7406</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>76545</t>
+          <t>3195</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>96726</t>
+          <t>14844</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>203335</t>
+          <t>18826</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>185849</t>
+          <t>11459</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>218839</t>
+          <t>28966</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -10612,112 +10612,112 @@
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Otros motivos</t>
+          <t>Propia voluntad</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>24163</t>
+          <t>116398</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>15901</t>
+          <t>104273</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>35097</t>
+          <t>127465</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>76</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>18320</t>
+          <t>86937</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>10059</t>
+          <t>76545</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>27629</t>
+          <t>96726</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>191</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>42483</t>
+          <t>203335</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>30982</t>
+          <t>185849</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>56770</t>
+          <t>218839</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>68,33%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>73,54%</t>
         </is>
       </c>
     </row>
@@ -10955,112 +10955,112 @@
       <c r="A30" s="1" t="n"/>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Preocupacion de sus efectos</t>
+          <t>Otros motivos</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>55</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>72502</t>
+          <t>57326</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>56420</t>
+          <t>44049</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>89752</t>
+          <t>73170</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>27462</t>
+          <t>43260</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>18835</t>
+          <t>30698</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>39684</t>
+          <t>57047</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>95</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>99964</t>
+          <t>100586</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>81514</t>
+          <t>81718</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>119615</t>
+          <t>119585</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,7%</t>
         </is>
       </c>
     </row>
@@ -11068,112 +11068,112 @@
       <c r="A31" s="1" t="n"/>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Disminucion del rendimiento físico/psíquico</t>
+          <t>Preocupacion de sus efectos</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>67</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>30384</t>
+          <t>72502</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>20699</t>
+          <t>56420</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>42437</t>
+          <t>89752</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>16107</t>
+          <t>27462</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>18835</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>25595</t>
+          <t>39684</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>94</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>46491</t>
+          <t>99964</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>34159</t>
+          <t>81514</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>61460</t>
+          <t>119615</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>12,71%</t>
         </is>
       </c>
     </row>
@@ -11181,112 +11181,112 @@
       <c r="A32" s="1" t="n"/>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Propia voluntad</t>
+          <t>Disminucion del rendimiento físico/psíquico</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>364322</t>
+          <t>30384</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>341105</t>
+          <t>20699</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>387069</t>
+          <t>42437</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>234281</t>
+          <t>16107</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>218497</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>250987</t>
+          <t>25595</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>598604</t>
+          <t>46491</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>567445</t>
+          <t>34159</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>628504</t>
+          <t>61460</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -11294,112 +11294,112 @@
       <c r="A33" s="1" t="n"/>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Otros motivos</t>
+          <t>Propia voluntad</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>353</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>57326</t>
+          <t>364322</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>44049</t>
+          <t>341105</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>73170</t>
+          <t>387069</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>218</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>43260</t>
+          <t>234281</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>30698</t>
+          <t>218497</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>57047</t>
+          <t>250987</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>571</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>100586</t>
+          <t>598604</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>81718</t>
+          <t>567445</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>119585</t>
+          <t>628504</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>66,77%</t>
         </is>
       </c>
     </row>
